--- a/Exam/gymtrackerpro/lib/controller/__tests__/it/user-controller/listMembers-it-form.xlsx
+++ b/Exam/gymtrackerpro/lib/controller/__tests__/it/user-controller/listMembers-it-form.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="63">
   <si>
     <t>Statement: listMembers(options?: MemberListOptions): Promise&lt;ActionResult&lt;PageResult&lt;MemberWithUser&gt;&gt;&gt; — delegates to userService.listMembers() and returns the paginated result wrapped in ActionResult.</t>
   </si>
@@ -117,6 +117,52 @@
   </si>
   <si>
     <t>{ success: true, data: { items: [], total: 0 } }</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seeded via userService.createMember(): Alice Smith (alice@gym.test), Bob Johnson (bob@gym.test).
+const options: MemberListOptions = { search: "alice@gym.test" }</t>
+  </si>
+  <si>
+    <t>{ success: true, data: { total: 1, items: [{ user: { email: "alice@gym.test" } }] } }</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seeded via userService.createMember(): Alice Smith (alice@gym.test), Bob Johnson (bob@gym.test).
+const options: MemberListOptions = { page: 1, pageSize: 100 }</t>
+  </si>
+  <si>
+    <t>{ success: true, data: { total: 2, items: array of length 2 } }</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seeded via userService.createMember(): Alice Smith (alice@gym.test).
+const options: MemberListOptions = { search: "%" }</t>
+  </si>
+  <si>
+    <t>{ success: true, data: { total: 0, items: [] } }</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seeded via userService.createMember(): Alice Smith (alice@gym.test), Bob Johnson (bob@gym.test), Charlie Brown (charlie@gym.test) — unique phones.
+const optionsP1: MemberListOptions = { page: 1, pageSize: 2 }
+const optionsP2: MemberListOptions = { page: 2, pageSize: 2 }</t>
+  </si>
+  <si>
+    <t>listMembers(optionsP1) then listMembers(optionsP2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Page 1: { success: true, data: { total: 3, items: array of length 2 } }
+Page 2: { success: true, data: { total: 3, items: array of length 1 } }
+No id appears in both pages</t>
   </si>
   <si>
     <t>Testing</t>
@@ -801,13 +847,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="80" customWidth="1"/>
-    <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="76" customWidth="1"/>
+    <col min="4" max="4" width="54" customWidth="1"/>
+    <col min="5" max="5" width="80" customWidth="1"/>
     <col min="6" max="6" width="27" customWidth="1"/>
     <col min="7" max="7" width="17" customWidth="1"/>
   </cols>
@@ -901,6 +947,98 @@
         <v>25</v>
       </c>
       <c r="G4" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" ht="65" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="6" t="s">
         <v>26</v>
       </c>
     </row>
@@ -929,17 +1067,17 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -951,40 +1089,40 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -992,40 +1130,40 @@
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="C6" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D6" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
